--- a/Oktober-2026.xlsx
+++ b/Oktober-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B81D81-E998-4446-A82E-4F97717A6F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE97B3B8-56BB-4D10-B768-F74E6148FC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -574,19 +574,18 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>253</v>
+        <v>315</v>
       </c>
       <c r="C2" s="4">
-        <v>552</v>
+        <v>711</v>
       </c>
       <c r="D2" s="9">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" s="13">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
       <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -594,19 +593,18 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="C3" s="4">
-        <v>498</v>
+        <v>847</v>
       </c>
       <c r="D3" s="9">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E3" s="13">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
       <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -614,19 +612,18 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>202</v>
+        <v>324</v>
       </c>
       <c r="C4" s="4">
-        <v>549</v>
+        <v>911</v>
       </c>
       <c r="D4" s="9">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E4" s="13">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
       <c r="H4" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -634,19 +631,18 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>218</v>
+        <v>310</v>
       </c>
       <c r="C5" s="4">
-        <v>561</v>
+        <v>785</v>
       </c>
       <c r="D5" s="9">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E5" s="13">
-        <v>2.5714285714285716</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
       <c r="H5" s="16"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -654,19 +650,18 @@
         <v>22</v>
       </c>
       <c r="B6" s="4">
-        <v>259</v>
+        <v>399</v>
       </c>
       <c r="C6" s="4">
-        <v>442</v>
+        <v>766</v>
       </c>
       <c r="D6" s="9">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E6" s="13">
-        <v>3.7142857142857144</v>
+        <v>3.5</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
       <c r="H6" s="16"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -674,19 +669,18 @@
         <v>23</v>
       </c>
       <c r="B7" s="4">
-        <v>206</v>
+        <v>265</v>
       </c>
       <c r="C7" s="4">
-        <v>598</v>
+        <v>778</v>
       </c>
       <c r="D7" s="9">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E7" s="13">
-        <v>2.1428571428571428</v>
+        <v>2.1</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
       <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -694,19 +688,18 @@
         <v>9</v>
       </c>
       <c r="B8" s="4">
-        <v>206</v>
+        <v>320</v>
       </c>
       <c r="C8" s="4">
-        <v>477</v>
+        <v>815</v>
       </c>
       <c r="D8" s="9">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E8" s="13">
-        <v>1.7142857142857142</v>
+        <v>2.6</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
       <c r="H8" s="16"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -714,19 +707,18 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>218</v>
+        <v>279</v>
       </c>
       <c r="C9" s="4">
-        <v>612</v>
+        <v>775</v>
       </c>
       <c r="D9" s="9">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E9" s="13">
-        <v>2.1428571428571428</v>
+        <v>2.1</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
       <c r="H9" s="16"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -734,19 +726,18 @@
         <v>11</v>
       </c>
       <c r="B10" s="4">
-        <v>200</v>
+        <v>305</v>
       </c>
       <c r="C10" s="4">
-        <v>478</v>
+        <v>738</v>
       </c>
       <c r="D10" s="9">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E10" s="13">
-        <v>2.1428571428571428</v>
+        <v>1.8</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
       <c r="H10" s="16"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -754,19 +745,18 @@
         <v>12</v>
       </c>
       <c r="B11" s="4">
-        <v>136</v>
+        <v>239</v>
       </c>
       <c r="C11" s="4">
-        <v>438</v>
+        <v>780</v>
       </c>
       <c r="D11" s="9">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="E11" s="13">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
       <c r="H11" s="16"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -774,19 +764,18 @@
         <v>13</v>
       </c>
       <c r="B12" s="4">
-        <v>229</v>
+        <v>354</v>
       </c>
       <c r="C12" s="4">
-        <v>425</v>
+        <v>743</v>
       </c>
       <c r="D12" s="9">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="E12" s="13">
-        <v>3.4285714285714284</v>
+        <v>3.7</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
       <c r="H12" s="16"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -794,19 +783,18 @@
         <v>14</v>
       </c>
       <c r="B13" s="4">
-        <v>147</v>
+        <v>243</v>
       </c>
       <c r="C13" s="4">
-        <v>338</v>
+        <v>652</v>
       </c>
       <c r="D13" s="9">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E13" s="13">
-        <v>3.1428571428571428</v>
+        <v>3.3</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
       <c r="H13" s="16"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -814,19 +802,18 @@
         <v>15</v>
       </c>
       <c r="B14" s="4">
-        <v>190</v>
+        <v>251</v>
       </c>
       <c r="C14" s="4">
-        <v>487</v>
+        <v>650</v>
       </c>
       <c r="D14" s="9">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E14" s="13">
-        <v>2.1428571428571428</v>
+        <v>2.1</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
       <c r="H14" s="16"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -834,19 +821,18 @@
         <v>16</v>
       </c>
       <c r="B15" s="4">
-        <v>140</v>
+        <v>197</v>
       </c>
       <c r="C15" s="4">
-        <v>588</v>
+        <v>842</v>
       </c>
       <c r="D15" s="9">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E15" s="13">
-        <v>1.8571428571428572</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
       <c r="H15" s="16"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -854,19 +840,18 @@
         <v>24</v>
       </c>
       <c r="B16" s="4">
-        <v>252</v>
+        <v>329</v>
       </c>
       <c r="C16" s="4">
-        <v>569</v>
+        <v>825</v>
       </c>
       <c r="D16" s="9">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E16" s="13">
-        <v>3.8571428571428572</v>
+        <v>4.3</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
       <c r="H16" s="16"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -874,19 +859,18 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="C17" s="4">
-        <v>552</v>
+        <v>636</v>
       </c>
       <c r="D17" s="9">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E17" s="13">
-        <v>1.4285714285714286</v>
+        <v>1.8</v>
       </c>
       <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
       <c r="H17" s="16"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -894,19 +878,18 @@
         <v>18</v>
       </c>
       <c r="B18" s="4">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="C18" s="4">
-        <v>640</v>
+        <v>836</v>
       </c>
       <c r="D18" s="9">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E18" s="13">
-        <v>1.7142857142857142</v>
+        <v>1.4</v>
       </c>
       <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
       <c r="H18" s="16"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -914,18 +897,17 @@
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>162</v>
+        <v>259</v>
       </c>
       <c r="C19" s="4">
-        <v>484</v>
+        <v>821</v>
       </c>
       <c r="D19" s="9">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E19" s="13">
-        <v>2.7142857142857144</v>
-      </c>
-      <c r="G19" s="1"/>
+        <v>3.1</v>
+      </c>
       <c r="H19" s="16"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -933,18 +915,17 @@
         <v>21</v>
       </c>
       <c r="B20" s="6">
-        <v>3443</v>
+        <v>4945</v>
       </c>
       <c r="C20" s="6">
-        <v>9288</v>
+        <v>13911</v>
       </c>
       <c r="D20" s="10">
-        <v>306</v>
+        <v>471</v>
       </c>
       <c r="E20" s="14">
-        <v>2.4285714285714288</v>
-      </c>
-      <c r="G20" s="1"/>
+        <v>2.6166666666666667</v>
+      </c>
       <c r="H20" s="16"/>
       <c r="I20" s="15"/>
     </row>
@@ -1004,7 +985,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E19">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G20">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1025,9 +1018,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="7" bestFit="1" customWidth="1"/>
     <col min="12" max="31" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="7.140625" customWidth="1"/>
     <col min="33" max="33" width="11.140625" bestFit="1" customWidth="1"/>
@@ -1165,11 +1156,19 @@
       <c r="J2" s="4">
         <v>108</v>
       </c>
-      <c r="K2" s="4"/>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
       <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>99</v>
+      </c>
+      <c r="O2" s="4">
+        <v>122</v>
+      </c>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
@@ -1188,7 +1187,7 @@
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
       <c r="AG2" s="9">
-        <v>805</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1222,11 +1221,19 @@
       <c r="J3" s="4">
         <v>101</v>
       </c>
-      <c r="K3" s="4"/>
+      <c r="K3" s="4">
+        <v>127</v>
+      </c>
       <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="M3" s="4">
+        <v>101</v>
+      </c>
+      <c r="N3" s="4">
+        <v>102</v>
+      </c>
+      <c r="O3" s="4">
+        <v>105</v>
+      </c>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
@@ -1245,7 +1252,7 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="9">
-        <v>644</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1253,7 +1260,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C4" s="4">
         <v>0</v>
@@ -1265,25 +1272,33 @@
         <v>0</v>
       </c>
       <c r="F4" s="4">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G4" s="4">
         <v>116</v>
       </c>
       <c r="H4" s="4">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I4" s="4">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="4">
         <v>0</v>
       </c>
-      <c r="K4" s="4"/>
+      <c r="K4" s="4">
+        <v>123</v>
+      </c>
       <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
+      <c r="M4" s="4">
+        <v>125</v>
+      </c>
+      <c r="N4" s="4">
+        <v>129</v>
+      </c>
+      <c r="O4" s="4">
+        <v>111</v>
+      </c>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
@@ -1302,7 +1317,7 @@
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="9">
-        <v>751</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1336,11 +1351,19 @@
       <c r="J5" s="4">
         <v>99</v>
       </c>
-      <c r="K5" s="4"/>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
       <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
+      <c r="M5" s="4">
+        <v>107</v>
+      </c>
+      <c r="N5" s="4">
+        <v>102</v>
+      </c>
+      <c r="O5" s="4">
+        <v>107</v>
+      </c>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
@@ -1359,7 +1382,7 @@
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="9">
-        <v>779</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1393,11 +1416,19 @@
       <c r="J6" s="4">
         <v>108</v>
       </c>
-      <c r="K6" s="4"/>
+      <c r="K6" s="4">
+        <v>129</v>
+      </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
+      <c r="M6" s="4">
+        <v>109</v>
+      </c>
+      <c r="N6" s="4">
+        <v>107</v>
+      </c>
+      <c r="O6" s="4">
+        <v>119</v>
+      </c>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
@@ -1416,7 +1447,7 @@
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="9">
-        <v>701</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1430,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="4">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E7" s="4">
         <v>0</v>
@@ -1450,11 +1481,19 @@
       <c r="J7" s="4">
         <v>94</v>
       </c>
-      <c r="K7" s="4"/>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
       <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
+      <c r="M7" s="4">
+        <v>123</v>
+      </c>
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>117</v>
+      </c>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
@@ -1473,7 +1512,7 @@
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="9">
-        <v>804</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1507,11 +1546,19 @@
       <c r="J8" s="4">
         <v>110</v>
       </c>
-      <c r="K8" s="4"/>
+      <c r="K8" s="4">
+        <v>127</v>
+      </c>
       <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
+      <c r="M8" s="4">
+        <v>115</v>
+      </c>
+      <c r="N8" s="4">
+        <v>104</v>
+      </c>
+      <c r="O8" s="4">
+        <v>106</v>
+      </c>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
@@ -1530,7 +1577,7 @@
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
       <c r="AG8" s="9">
-        <v>683</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1538,7 +1585,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" s="4">
         <v>0</v>
@@ -1564,11 +1611,19 @@
       <c r="J9" s="4">
         <v>103</v>
       </c>
-      <c r="K9" s="4"/>
+      <c r="K9" s="4">
+        <v>0</v>
+      </c>
       <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
+      <c r="M9" s="4">
+        <v>105</v>
+      </c>
+      <c r="N9" s="4">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4">
+        <v>120</v>
+      </c>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
@@ -1587,7 +1642,7 @@
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
       <c r="AG9" s="9">
-        <v>830</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1621,11 +1676,19 @@
       <c r="J10" s="4">
         <v>0</v>
       </c>
-      <c r="K10" s="4"/>
+      <c r="K10" s="4">
+        <v>131</v>
+      </c>
       <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
+      <c r="M10" s="4">
+        <v>126</v>
+      </c>
+      <c r="N10" s="4">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4">
+        <v>108</v>
+      </c>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
@@ -1644,7 +1707,7 @@
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
       <c r="AG10" s="9">
-        <v>678</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1678,11 +1741,19 @@
       <c r="J11" s="4">
         <v>121</v>
       </c>
-      <c r="K11" s="4"/>
+      <c r="K11" s="4">
+        <v>121</v>
+      </c>
       <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
+      <c r="M11" s="4">
+        <v>106</v>
+      </c>
+      <c r="N11" s="4">
+        <v>107</v>
+      </c>
+      <c r="O11" s="4">
+        <v>111</v>
+      </c>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
@@ -1701,7 +1772,7 @@
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
       <c r="AG11" s="9">
-        <v>574</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -1735,11 +1806,19 @@
       <c r="J12" s="4">
         <v>107</v>
       </c>
-      <c r="K12" s="4"/>
+      <c r="K12" s="4">
+        <v>120</v>
+      </c>
       <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
+      <c r="M12" s="4">
+        <v>110</v>
+      </c>
+      <c r="N12" s="4">
+        <v>106</v>
+      </c>
+      <c r="O12" s="4">
+        <v>107</v>
+      </c>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
@@ -1758,7 +1837,7 @@
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="9">
-        <v>654</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -1778,10 +1857,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="4">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G13" s="4">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H13" s="4">
         <v>99</v>
@@ -1792,11 +1871,19 @@
       <c r="J13" s="4">
         <v>97</v>
       </c>
-      <c r="K13" s="4"/>
+      <c r="K13" s="4">
+        <v>98</v>
+      </c>
       <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
+      <c r="M13" s="4">
+        <v>108</v>
+      </c>
+      <c r="N13" s="4">
+        <v>101</v>
+      </c>
+      <c r="O13" s="4">
+        <v>105</v>
+      </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
@@ -1815,7 +1902,7 @@
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="9">
-        <v>485</v>
+        <v>895</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -1849,11 +1936,19 @@
       <c r="J14" s="4">
         <v>0</v>
       </c>
-      <c r="K14" s="4"/>
+      <c r="K14" s="4">
+        <v>1</v>
+      </c>
       <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
+      <c r="M14" s="4">
+        <v>114</v>
+      </c>
+      <c r="N14" s="4">
+        <v>109</v>
+      </c>
+      <c r="O14" s="4">
+        <v>0</v>
+      </c>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
@@ -1872,7 +1967,7 @@
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
       <c r="AG14" s="9">
-        <v>677</v>
+        <v>901</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -1906,11 +2001,19 @@
       <c r="J15" s="4">
         <v>95</v>
       </c>
-      <c r="K15" s="4"/>
+      <c r="K15" s="4">
+        <v>107</v>
+      </c>
       <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
+      <c r="M15" s="4">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4">
+        <v>102</v>
+      </c>
+      <c r="O15" s="4">
+        <v>102</v>
+      </c>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
@@ -1929,7 +2032,7 @@
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="9">
-        <v>728</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -1963,11 +2066,19 @@
       <c r="J16" s="4">
         <v>115</v>
       </c>
-      <c r="K16" s="4"/>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
       <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
+      <c r="M16" s="4">
+        <v>109</v>
+      </c>
+      <c r="N16" s="4">
+        <v>112</v>
+      </c>
+      <c r="O16" s="4">
+        <v>112</v>
+      </c>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
@@ -1986,7 +2097,7 @@
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
       <c r="AG16" s="9">
-        <v>821</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -2009,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H17" s="4">
         <v>108</v>
@@ -2020,11 +2131,19 @@
       <c r="J17" s="4">
         <v>108</v>
       </c>
-      <c r="K17" s="4"/>
+      <c r="K17" s="4">
+        <v>0</v>
+      </c>
       <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
+      <c r="M17" s="4">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4">
+        <v>105</v>
+      </c>
+      <c r="O17" s="4">
+        <v>0</v>
+      </c>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
@@ -2043,7 +2162,7 @@
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9">
-        <v>727</v>
+        <v>831</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -2077,11 +2196,19 @@
       <c r="J18" s="4">
         <v>105</v>
       </c>
-      <c r="K18" s="4"/>
+      <c r="K18" s="4">
+        <v>0</v>
+      </c>
       <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
+      <c r="M18" s="4">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4">
+        <v>112</v>
+      </c>
+      <c r="O18" s="4">
+        <v>109</v>
+      </c>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
@@ -2100,7 +2227,7 @@
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
       <c r="AG18" s="9">
-        <v>744</v>
+        <v>965</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -2108,10 +2235,10 @@
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C19" s="4">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D19" s="4">
         <v>0</v>
@@ -2134,11 +2261,19 @@
       <c r="J19" s="4">
         <v>105</v>
       </c>
-      <c r="K19" s="4"/>
+      <c r="K19" s="4">
+        <v>111</v>
+      </c>
       <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
+      <c r="M19" s="4">
+        <v>114</v>
+      </c>
+      <c r="N19" s="4">
+        <v>106</v>
+      </c>
+      <c r="O19" s="4">
+        <v>105</v>
+      </c>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
@@ -2157,7 +2292,7 @@
       <c r="AE19" s="4"/>
       <c r="AF19" s="4"/>
       <c r="AG19" s="9">
-        <v>646</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -2165,37 +2300,45 @@
         <v>21</v>
       </c>
       <c r="B20" s="6">
-        <v>1548</v>
+        <v>1545</v>
       </c>
       <c r="C20" s="6">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="D20" s="6">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="E20" s="6">
         <v>0</v>
       </c>
       <c r="F20" s="6">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="G20" s="6">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="H20" s="6">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="I20" s="6">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="J20" s="6">
         <v>1576</v>
       </c>
-      <c r="K20" s="6"/>
+      <c r="K20" s="6">
+        <v>1195</v>
+      </c>
       <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
+      <c r="M20" s="6">
+        <v>1572</v>
+      </c>
+      <c r="N20" s="6">
+        <v>1603</v>
+      </c>
+      <c r="O20" s="6">
+        <v>1766</v>
+      </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
@@ -2214,7 +2357,7 @@
       <c r="AE20" s="6"/>
       <c r="AF20" s="6"/>
       <c r="AG20" s="10">
-        <v>12731</v>
+        <v>18856</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
@@ -2281,7 +2424,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.4285714285714288</v>
+        <v>2.6166666666666667</v>
       </c>
       <c r="D2" s="1"/>
     </row>

--- a/Oktober-2026.xlsx
+++ b/Oktober-2026.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE97B3B8-56BB-4D10-B768-F74E6148FC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A998622-313E-4F41-9E20-2CE6D66805EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Trend" sheetId="2" r:id="rId2"/>
     <sheet name="Summary" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -574,16 +574,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="C2" s="4">
-        <v>711</v>
+        <v>767</v>
       </c>
       <c r="D2" s="9">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" s="13">
-        <v>1.7</v>
+        <v>1.7272727272727273</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="16"/>
@@ -593,16 +593,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="C3" s="4">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="D3" s="9">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E3" s="13">
-        <v>2.5</v>
+        <v>2.6363636363636362</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="16"/>
@@ -621,7 +621,7 @@
         <v>29</v>
       </c>
       <c r="E4" s="13">
-        <v>2.9</v>
+        <v>2.6363636363636362</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="16"/>
@@ -631,16 +631,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="C5" s="4">
-        <v>785</v>
+        <v>867</v>
       </c>
       <c r="D5" s="9">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E5" s="13">
-        <v>2.2999999999999998</v>
+        <v>2.5454545454545454</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="16"/>
@@ -650,16 +650,16 @@
         <v>22</v>
       </c>
       <c r="B6" s="4">
-        <v>399</v>
+        <v>438</v>
       </c>
       <c r="C6" s="4">
-        <v>766</v>
+        <v>846</v>
       </c>
       <c r="D6" s="9">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E6" s="13">
-        <v>3.5</v>
+        <v>3.5454545454545454</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="16"/>
@@ -669,16 +669,16 @@
         <v>23</v>
       </c>
       <c r="B7" s="4">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="C7" s="4">
-        <v>778</v>
+        <v>866</v>
       </c>
       <c r="D7" s="9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" s="13">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="16"/>
@@ -688,16 +688,16 @@
         <v>9</v>
       </c>
       <c r="B8" s="4">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="C8" s="4">
-        <v>815</v>
+        <v>901</v>
       </c>
       <c r="D8" s="9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" s="13">
-        <v>2.6</v>
+        <v>2.4545454545454546</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="16"/>
@@ -707,16 +707,16 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="C9" s="4">
-        <v>775</v>
+        <v>863</v>
       </c>
       <c r="D9" s="9">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E9" s="13">
-        <v>2.1</v>
+        <v>2.2727272727272729</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="16"/>
@@ -726,16 +726,16 @@
         <v>11</v>
       </c>
       <c r="B10" s="4">
-        <v>305</v>
+        <v>332</v>
       </c>
       <c r="C10" s="4">
-        <v>738</v>
+        <v>839</v>
       </c>
       <c r="D10" s="9">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E10" s="13">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="16"/>
@@ -754,7 +754,7 @@
         <v>36</v>
       </c>
       <c r="E11" s="13">
-        <v>3.6</v>
+        <v>3.2727272727272729</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="16"/>
@@ -764,16 +764,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="4">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="C12" s="4">
-        <v>743</v>
+        <v>820</v>
       </c>
       <c r="D12" s="9">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E12" s="13">
-        <v>3.7</v>
+        <v>3.5454545454545454</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="16"/>
@@ -783,16 +783,16 @@
         <v>14</v>
       </c>
       <c r="B13" s="4">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="C13" s="4">
-        <v>652</v>
+        <v>726</v>
       </c>
       <c r="D13" s="9">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E13" s="13">
-        <v>3.3</v>
+        <v>3.2727272727272729</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="16"/>
@@ -802,16 +802,16 @@
         <v>15</v>
       </c>
       <c r="B14" s="4">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="C14" s="4">
-        <v>650</v>
+        <v>738</v>
       </c>
       <c r="D14" s="9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E14" s="13">
-        <v>2.1</v>
+        <v>2.0909090909090908</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="16"/>
@@ -827,10 +827,10 @@
         <v>842</v>
       </c>
       <c r="D15" s="9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15" s="13">
-        <v>2.2999999999999998</v>
+        <v>2.1818181818181817</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="16"/>
@@ -846,10 +846,10 @@
         <v>825</v>
       </c>
       <c r="D16" s="9">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E16" s="13">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="16"/>
@@ -859,16 +859,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="C17" s="4">
-        <v>636</v>
+        <v>721</v>
       </c>
       <c r="D17" s="9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E17" s="13">
-        <v>1.8</v>
+        <v>1.7272727272727273</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="16"/>
@@ -878,16 +878,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="4">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C18" s="4">
-        <v>836</v>
+        <v>937</v>
       </c>
       <c r="D18" s="9">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E18" s="13">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="16"/>
@@ -897,16 +897,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="C19" s="4">
-        <v>821</v>
+        <v>908</v>
       </c>
       <c r="D19" s="9">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E19" s="13">
-        <v>3.1</v>
+        <v>3.3636363636363638</v>
       </c>
       <c r="H19" s="16"/>
     </row>
@@ -915,16 +915,16 @@
         <v>21</v>
       </c>
       <c r="B20" s="6">
-        <v>4945</v>
+        <v>5287</v>
       </c>
       <c r="C20" s="6">
-        <v>13911</v>
+        <v>15092</v>
       </c>
       <c r="D20" s="10">
-        <v>471</v>
+        <v>520</v>
       </c>
       <c r="E20" s="14">
-        <v>2.6166666666666667</v>
+        <v>2.6262626262626263</v>
       </c>
       <c r="H20" s="16"/>
       <c r="I20" s="15"/>
@@ -1159,7 +1159,9 @@
       <c r="K2" s="4">
         <v>0</v>
       </c>
-      <c r="L2" s="4"/>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
       <c r="M2" s="4">
         <v>0</v>
       </c>
@@ -1169,7 +1171,9 @@
       <c r="O2" s="4">
         <v>122</v>
       </c>
-      <c r="P2" s="4"/>
+      <c r="P2" s="4">
+        <v>86</v>
+      </c>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
@@ -1187,7 +1191,7 @@
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
       <c r="AG2" s="9">
-        <v>1026</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1224,7 +1228,9 @@
       <c r="K3" s="4">
         <v>127</v>
       </c>
-      <c r="L3" s="4"/>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
       <c r="M3" s="4">
         <v>101</v>
       </c>
@@ -1234,7 +1240,9 @@
       <c r="O3" s="4">
         <v>105</v>
       </c>
-      <c r="P3" s="4"/>
+      <c r="P3" s="4">
+        <v>108</v>
+      </c>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
@@ -1252,7 +1260,7 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="9">
-        <v>1079</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1289,7 +1297,9 @@
       <c r="K4" s="4">
         <v>123</v>
       </c>
-      <c r="L4" s="4"/>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
       <c r="M4" s="4">
         <v>125</v>
       </c>
@@ -1299,7 +1309,9 @@
       <c r="O4" s="4">
         <v>111</v>
       </c>
-      <c r="P4" s="4"/>
+      <c r="P4" s="4">
+        <v>0</v>
+      </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
@@ -1354,7 +1366,9 @@
       <c r="K5" s="4">
         <v>0</v>
       </c>
-      <c r="L5" s="4"/>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
       <c r="M5" s="4">
         <v>107</v>
       </c>
@@ -1364,7 +1378,9 @@
       <c r="O5" s="4">
         <v>107</v>
       </c>
-      <c r="P5" s="4"/>
+      <c r="P5" s="4">
+        <v>100</v>
+      </c>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
@@ -1382,7 +1398,7 @@
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="9">
-        <v>1095</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1419,7 +1435,9 @@
       <c r="K6" s="4">
         <v>129</v>
       </c>
-      <c r="L6" s="4"/>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
       <c r="M6" s="4">
         <v>109</v>
       </c>
@@ -1429,7 +1447,9 @@
       <c r="O6" s="4">
         <v>119</v>
       </c>
-      <c r="P6" s="4"/>
+      <c r="P6" s="4">
+        <v>119</v>
+      </c>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
@@ -1447,7 +1467,7 @@
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="9">
-        <v>1165</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1484,7 +1504,9 @@
       <c r="K7" s="4">
         <v>0</v>
       </c>
-      <c r="L7" s="4"/>
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
       <c r="M7" s="4">
         <v>123</v>
       </c>
@@ -1494,7 +1516,9 @@
       <c r="O7" s="4">
         <v>117</v>
       </c>
-      <c r="P7" s="4"/>
+      <c r="P7" s="4">
+        <v>114</v>
+      </c>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
@@ -1512,7 +1536,7 @@
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="9">
-        <v>1043</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1549,7 +1573,9 @@
       <c r="K8" s="4">
         <v>127</v>
       </c>
-      <c r="L8" s="4"/>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
       <c r="M8" s="4">
         <v>115</v>
       </c>
@@ -1559,7 +1585,9 @@
       <c r="O8" s="4">
         <v>106</v>
       </c>
-      <c r="P8" s="4"/>
+      <c r="P8" s="4">
+        <v>116</v>
+      </c>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
@@ -1577,7 +1605,7 @@
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
       <c r="AG8" s="9">
-        <v>1135</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1614,7 +1642,9 @@
       <c r="K9" s="4">
         <v>0</v>
       </c>
-      <c r="L9" s="4"/>
+      <c r="L9" s="4">
+        <v>0</v>
+      </c>
       <c r="M9" s="4">
         <v>105</v>
       </c>
@@ -1624,7 +1654,9 @@
       <c r="O9" s="4">
         <v>120</v>
       </c>
-      <c r="P9" s="4"/>
+      <c r="P9" s="4">
+        <v>119</v>
+      </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
@@ -1642,7 +1674,7 @@
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
       <c r="AG9" s="9">
-        <v>1054</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1679,7 +1711,9 @@
       <c r="K10" s="4">
         <v>131</v>
       </c>
-      <c r="L10" s="4"/>
+      <c r="L10" s="4">
+        <v>0</v>
+      </c>
       <c r="M10" s="4">
         <v>126</v>
       </c>
@@ -1689,7 +1723,9 @@
       <c r="O10" s="4">
         <v>108</v>
       </c>
-      <c r="P10" s="4"/>
+      <c r="P10" s="4">
+        <v>128</v>
+      </c>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
@@ -1707,7 +1743,7 @@
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
       <c r="AG10" s="9">
-        <v>1043</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1744,7 +1780,9 @@
       <c r="K11" s="4">
         <v>121</v>
       </c>
-      <c r="L11" s="4"/>
+      <c r="L11" s="4">
+        <v>0</v>
+      </c>
       <c r="M11" s="4">
         <v>106</v>
       </c>
@@ -1754,7 +1792,9 @@
       <c r="O11" s="4">
         <v>111</v>
       </c>
-      <c r="P11" s="4"/>
+      <c r="P11" s="4">
+        <v>0</v>
+      </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
@@ -1809,7 +1849,9 @@
       <c r="K12" s="4">
         <v>120</v>
       </c>
-      <c r="L12" s="4"/>
+      <c r="L12" s="4">
+        <v>0</v>
+      </c>
       <c r="M12" s="4">
         <v>110</v>
       </c>
@@ -1819,7 +1861,9 @@
       <c r="O12" s="4">
         <v>107</v>
       </c>
-      <c r="P12" s="4"/>
+      <c r="P12" s="4">
+        <v>107</v>
+      </c>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
@@ -1837,7 +1881,7 @@
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="9">
-        <v>1097</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -1874,7 +1918,9 @@
       <c r="K13" s="4">
         <v>98</v>
       </c>
-      <c r="L13" s="4"/>
+      <c r="L13" s="4">
+        <v>0</v>
+      </c>
       <c r="M13" s="4">
         <v>108</v>
       </c>
@@ -1884,7 +1930,9 @@
       <c r="O13" s="4">
         <v>105</v>
       </c>
-      <c r="P13" s="4"/>
+      <c r="P13" s="4">
+        <v>92</v>
+      </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
@@ -1902,7 +1950,7 @@
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="9">
-        <v>895</v>
+        <v>987</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -1939,7 +1987,9 @@
       <c r="K14" s="4">
         <v>1</v>
       </c>
-      <c r="L14" s="4"/>
+      <c r="L14" s="4">
+        <v>0</v>
+      </c>
       <c r="M14" s="4">
         <v>114</v>
       </c>
@@ -1949,7 +1999,9 @@
       <c r="O14" s="4">
         <v>0</v>
       </c>
-      <c r="P14" s="4"/>
+      <c r="P14" s="4">
+        <v>107</v>
+      </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
@@ -1967,7 +2019,7 @@
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
       <c r="AG14" s="9">
-        <v>901</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -2004,7 +2056,9 @@
       <c r="K15" s="4">
         <v>107</v>
       </c>
-      <c r="L15" s="4"/>
+      <c r="L15" s="4">
+        <v>0</v>
+      </c>
       <c r="M15" s="4">
         <v>0</v>
       </c>
@@ -2014,7 +2068,9 @@
       <c r="O15" s="4">
         <v>102</v>
       </c>
-      <c r="P15" s="4"/>
+      <c r="P15" s="4">
+        <v>0</v>
+      </c>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
@@ -2069,7 +2125,9 @@
       <c r="K16" s="4">
         <v>0</v>
       </c>
-      <c r="L16" s="4"/>
+      <c r="L16" s="4">
+        <v>0</v>
+      </c>
       <c r="M16" s="4">
         <v>109</v>
       </c>
@@ -2079,7 +2137,9 @@
       <c r="O16" s="4">
         <v>112</v>
       </c>
-      <c r="P16" s="4"/>
+      <c r="P16" s="4">
+        <v>0</v>
+      </c>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
@@ -2134,7 +2194,9 @@
       <c r="K17" s="4">
         <v>0</v>
       </c>
-      <c r="L17" s="4"/>
+      <c r="L17" s="4">
+        <v>0</v>
+      </c>
       <c r="M17" s="4">
         <v>0</v>
       </c>
@@ -2144,7 +2206,9 @@
       <c r="O17" s="4">
         <v>0</v>
       </c>
-      <c r="P17" s="4"/>
+      <c r="P17" s="4">
+        <v>103</v>
+      </c>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
@@ -2162,7 +2226,7 @@
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9">
-        <v>831</v>
+        <v>934</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -2199,7 +2263,9 @@
       <c r="K18" s="4">
         <v>0</v>
       </c>
-      <c r="L18" s="4"/>
+      <c r="L18" s="4">
+        <v>0</v>
+      </c>
       <c r="M18" s="4">
         <v>0</v>
       </c>
@@ -2209,7 +2275,9 @@
       <c r="O18" s="4">
         <v>109</v>
       </c>
-      <c r="P18" s="4"/>
+      <c r="P18" s="4">
+        <v>110</v>
+      </c>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
@@ -2227,7 +2295,7 @@
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
       <c r="AG18" s="9">
-        <v>965</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -2264,7 +2332,9 @@
       <c r="K19" s="4">
         <v>111</v>
       </c>
-      <c r="L19" s="4"/>
+      <c r="L19" s="4">
+        <v>0</v>
+      </c>
       <c r="M19" s="4">
         <v>114</v>
       </c>
@@ -2274,7 +2344,9 @@
       <c r="O19" s="4">
         <v>105</v>
       </c>
-      <c r="P19" s="4"/>
+      <c r="P19" s="4">
+        <v>114</v>
+      </c>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
@@ -2292,7 +2364,7 @@
       <c r="AE19" s="4"/>
       <c r="AF19" s="4"/>
       <c r="AG19" s="9">
-        <v>1080</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -2329,7 +2401,9 @@
       <c r="K20" s="6">
         <v>1195</v>
       </c>
-      <c r="L20" s="6"/>
+      <c r="L20" s="6">
+        <v>0</v>
+      </c>
       <c r="M20" s="6">
         <v>1572</v>
       </c>
@@ -2339,7 +2413,9 @@
       <c r="O20" s="6">
         <v>1766</v>
       </c>
-      <c r="P20" s="6"/>
+      <c r="P20" s="6">
+        <v>1523</v>
+      </c>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
       <c r="S20" s="6"/>
@@ -2357,7 +2433,7 @@
       <c r="AE20" s="6"/>
       <c r="AF20" s="6"/>
       <c r="AG20" s="10">
-        <v>18856</v>
+        <v>20379</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
@@ -2424,7 +2500,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.6166666666666667</v>
+        <v>2.6262626262626263</v>
       </c>
       <c r="D2" s="1"/>
     </row>

--- a/Oktober-2026.xlsx
+++ b/Oktober-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A998622-313E-4F41-9E20-2CE6D66805EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A240F2D-E0C0-47D1-9589-A2805E2F8FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -574,16 +574,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="C2" s="4">
-        <v>767</v>
+        <v>832</v>
       </c>
       <c r="D2" s="9">
         <v>19</v>
       </c>
       <c r="E2" s="13">
-        <v>1.7272727272727273</v>
+        <v>2.5</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="16"/>
@@ -593,16 +593,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="C3" s="4">
-        <v>935</v>
+        <v>1021</v>
       </c>
       <c r="D3" s="9">
         <v>29</v>
       </c>
       <c r="E3" s="13">
-        <v>2.6363636363636362</v>
+        <v>3</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="16"/>
@@ -612,16 +612,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>324</v>
+        <v>380</v>
       </c>
       <c r="C4" s="4">
-        <v>911</v>
+        <v>1086</v>
       </c>
       <c r="D4" s="9">
         <v>29</v>
       </c>
       <c r="E4" s="13">
-        <v>2.6363636363636362</v>
+        <v>3.5</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="16"/>
@@ -631,16 +631,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C5" s="4">
-        <v>867</v>
+        <v>963</v>
       </c>
       <c r="D5" s="9">
         <v>28</v>
       </c>
       <c r="E5" s="13">
-        <v>2.5454545454545454</v>
+        <v>2.5</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="16"/>
@@ -650,16 +650,16 @@
         <v>22</v>
       </c>
       <c r="B6" s="4">
-        <v>438</v>
+        <v>467</v>
       </c>
       <c r="C6" s="4">
-        <v>846</v>
+        <v>929</v>
       </c>
       <c r="D6" s="9">
         <v>39</v>
       </c>
       <c r="E6" s="13">
-        <v>3.5454545454545454</v>
+        <v>3.75</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="16"/>
@@ -669,16 +669,16 @@
         <v>23</v>
       </c>
       <c r="B7" s="4">
-        <v>291</v>
+        <v>347</v>
       </c>
       <c r="C7" s="4">
-        <v>866</v>
+        <v>1009</v>
       </c>
       <c r="D7" s="9">
         <v>22</v>
       </c>
       <c r="E7" s="13">
-        <v>2</v>
+        <v>2.5833333333333335</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="16"/>
@@ -688,16 +688,16 @@
         <v>9</v>
       </c>
       <c r="B8" s="4">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="C8" s="4">
-        <v>901</v>
+        <v>982</v>
       </c>
       <c r="D8" s="9">
         <v>27</v>
       </c>
       <c r="E8" s="13">
-        <v>2.4545454545454546</v>
+        <v>2.9166666666666665</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="16"/>
@@ -707,16 +707,16 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>310</v>
+        <v>362</v>
       </c>
       <c r="C9" s="4">
-        <v>863</v>
+        <v>1031</v>
       </c>
       <c r="D9" s="9">
         <v>25</v>
       </c>
       <c r="E9" s="13">
-        <v>2.2727272727272729</v>
+        <v>3</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="16"/>
@@ -726,16 +726,16 @@
         <v>11</v>
       </c>
       <c r="B10" s="4">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="C10" s="4">
-        <v>839</v>
+        <v>915</v>
       </c>
       <c r="D10" s="9">
         <v>22</v>
       </c>
       <c r="E10" s="13">
-        <v>2</v>
+        <v>2.5833333333333335</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="16"/>
@@ -745,16 +745,16 @@
         <v>12</v>
       </c>
       <c r="B11" s="4">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="C11" s="4">
-        <v>780</v>
+        <v>860</v>
       </c>
       <c r="D11" s="9">
         <v>36</v>
       </c>
       <c r="E11" s="13">
-        <v>3.2727272727272729</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="16"/>
@@ -764,16 +764,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="4">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="C12" s="4">
-        <v>820</v>
+        <v>914</v>
       </c>
       <c r="D12" s="9">
         <v>39</v>
       </c>
       <c r="E12" s="13">
-        <v>3.5454545454545454</v>
+        <v>4.083333333333333</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="16"/>
@@ -783,16 +783,16 @@
         <v>14</v>
       </c>
       <c r="B13" s="4">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C13" s="4">
-        <v>726</v>
+        <v>812</v>
       </c>
       <c r="D13" s="9">
         <v>36</v>
       </c>
       <c r="E13" s="13">
-        <v>3.2727272727272729</v>
+        <v>3.75</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="16"/>
@@ -802,16 +802,16 @@
         <v>15</v>
       </c>
       <c r="B14" s="4">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="C14" s="4">
-        <v>738</v>
+        <v>912</v>
       </c>
       <c r="D14" s="9">
         <v>23</v>
       </c>
       <c r="E14" s="13">
-        <v>2.0909090909090908</v>
+        <v>2.75</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="16"/>
@@ -821,16 +821,16 @@
         <v>16</v>
       </c>
       <c r="B15" s="4">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="C15" s="4">
-        <v>842</v>
+        <v>930</v>
       </c>
       <c r="D15" s="9">
         <v>24</v>
       </c>
       <c r="E15" s="13">
-        <v>2.1818181818181817</v>
+        <v>2.5</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="16"/>
@@ -840,16 +840,16 @@
         <v>24</v>
       </c>
       <c r="B16" s="4">
-        <v>329</v>
+        <v>397</v>
       </c>
       <c r="C16" s="4">
-        <v>825</v>
+        <v>976</v>
       </c>
       <c r="D16" s="9">
         <v>44</v>
       </c>
       <c r="E16" s="13">
-        <v>4</v>
+        <v>4.916666666666667</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="16"/>
@@ -859,16 +859,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>213</v>
+        <v>275</v>
       </c>
       <c r="C17" s="4">
-        <v>721</v>
+        <v>883</v>
       </c>
       <c r="D17" s="9">
         <v>19</v>
       </c>
       <c r="E17" s="13">
-        <v>1.7272727272727273</v>
+        <v>2.1666666666666665</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="16"/>
@@ -878,16 +878,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="4">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C18" s="4">
-        <v>937</v>
+        <v>1030</v>
       </c>
       <c r="D18" s="9">
         <v>22</v>
       </c>
       <c r="E18" s="13">
-        <v>2</v>
+        <v>2.0833333333333335</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="16"/>
@@ -897,16 +897,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="C19" s="4">
-        <v>908</v>
+        <v>997</v>
       </c>
       <c r="D19" s="9">
         <v>37</v>
       </c>
       <c r="E19" s="13">
-        <v>3.3636363636363638</v>
+        <v>3.5833333333333335</v>
       </c>
       <c r="H19" s="16"/>
     </row>
@@ -915,16 +915,16 @@
         <v>21</v>
       </c>
       <c r="B20" s="6">
-        <v>5287</v>
+        <v>5897</v>
       </c>
       <c r="C20" s="6">
-        <v>15092</v>
+        <v>17082</v>
       </c>
       <c r="D20" s="10">
         <v>520</v>
       </c>
       <c r="E20" s="14">
-        <v>2.6262626262626263</v>
+        <v>3.1018518518518521</v>
       </c>
       <c r="H20" s="16"/>
       <c r="I20" s="15"/>
@@ -1174,8 +1174,12 @@
       <c r="P2" s="4">
         <v>86</v>
       </c>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
+      <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
+        <v>106</v>
+      </c>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
@@ -1191,7 +1195,7 @@
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
       <c r="AG2" s="9">
-        <v>1112</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1243,8 +1247,12 @@
       <c r="P3" s="4">
         <v>108</v>
       </c>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
+      <c r="Q3" s="4">
+        <v>106</v>
+      </c>
+      <c r="R3" s="4">
+        <v>0</v>
+      </c>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
@@ -1260,7 +1268,7 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="9">
-        <v>1187</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1312,8 +1320,12 @@
       <c r="P4" s="4">
         <v>0</v>
       </c>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
+      <c r="Q4" s="4">
+        <v>112</v>
+      </c>
+      <c r="R4" s="4">
+        <v>119</v>
+      </c>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
@@ -1329,7 +1341,7 @@
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="9">
-        <v>1235</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1381,8 +1393,12 @@
       <c r="P5" s="4">
         <v>100</v>
       </c>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
+      <c r="Q5" s="4">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4">
+        <v>124</v>
+      </c>
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
@@ -1398,7 +1414,7 @@
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="9">
-        <v>1195</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1450,8 +1466,12 @@
       <c r="P6" s="4">
         <v>119</v>
       </c>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
+      <c r="Q6" s="4">
+        <v>112</v>
+      </c>
+      <c r="R6" s="4">
+        <v>0</v>
+      </c>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
@@ -1467,7 +1487,7 @@
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="9">
-        <v>1284</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1519,8 +1539,12 @@
       <c r="P7" s="4">
         <v>114</v>
       </c>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
+      <c r="Q7" s="4">
+        <v>111</v>
+      </c>
+      <c r="R7" s="4">
+        <v>88</v>
+      </c>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
@@ -1536,7 +1560,7 @@
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="9">
-        <v>1157</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1588,8 +1612,12 @@
       <c r="P8" s="4">
         <v>116</v>
       </c>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
+      <c r="Q8" s="4">
+        <v>106</v>
+      </c>
+      <c r="R8" s="4">
+        <v>0</v>
+      </c>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
@@ -1605,7 +1633,7 @@
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
       <c r="AG8" s="9">
-        <v>1251</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1657,8 +1685,12 @@
       <c r="P9" s="4">
         <v>119</v>
       </c>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
+      <c r="Q9" s="4">
+        <v>110</v>
+      </c>
+      <c r="R9" s="4">
+        <v>110</v>
+      </c>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
@@ -1674,7 +1706,7 @@
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
       <c r="AG9" s="9">
-        <v>1173</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1726,8 +1758,12 @@
       <c r="P10" s="4">
         <v>128</v>
       </c>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
+      <c r="Q10" s="4">
+        <v>104</v>
+      </c>
+      <c r="R10" s="4">
+        <v>0</v>
+      </c>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
@@ -1743,7 +1779,7 @@
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
       <c r="AG10" s="9">
-        <v>1171</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1795,8 +1831,12 @@
       <c r="P11" s="4">
         <v>0</v>
       </c>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
+      <c r="Q11" s="4">
+        <v>107</v>
+      </c>
+      <c r="R11" s="4">
+        <v>0</v>
+      </c>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
@@ -1812,7 +1852,7 @@
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
       <c r="AG11" s="9">
-        <v>1019</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -1864,8 +1904,12 @@
       <c r="P12" s="4">
         <v>107</v>
       </c>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
+      <c r="Q12" s="4">
+        <v>112</v>
+      </c>
+      <c r="R12" s="4">
+        <v>0</v>
+      </c>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
@@ -1881,7 +1925,7 @@
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="9">
-        <v>1204</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -1933,8 +1977,12 @@
       <c r="P13" s="4">
         <v>92</v>
       </c>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
+      <c r="Q13" s="4">
+        <v>104</v>
+      </c>
+      <c r="R13" s="4">
+        <v>0</v>
+      </c>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
@@ -1950,7 +1998,7 @@
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="9">
-        <v>987</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -2002,8 +2050,12 @@
       <c r="P14" s="4">
         <v>107</v>
       </c>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
+      <c r="Q14" s="4">
+        <v>103</v>
+      </c>
+      <c r="R14" s="4">
+        <v>110</v>
+      </c>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
@@ -2019,7 +2071,7 @@
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
       <c r="AG14" s="9">
-        <v>1008</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -2071,8 +2123,12 @@
       <c r="P15" s="4">
         <v>0</v>
       </c>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
+      <c r="Q15" s="4">
+        <v>99</v>
+      </c>
+      <c r="R15" s="4">
+        <v>0</v>
+      </c>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
@@ -2088,7 +2144,7 @@
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="9">
-        <v>1039</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -2140,8 +2196,12 @@
       <c r="P16" s="4">
         <v>0</v>
       </c>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
+      <c r="Q16" s="4">
+        <v>108</v>
+      </c>
+      <c r="R16" s="4">
+        <v>111</v>
+      </c>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
       <c r="U16" s="4"/>
@@ -2157,7 +2217,7 @@
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
       <c r="AG16" s="9">
-        <v>1154</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -2209,8 +2269,12 @@
       <c r="P17" s="4">
         <v>103</v>
       </c>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
+      <c r="Q17" s="4">
+        <v>108</v>
+      </c>
+      <c r="R17" s="4">
+        <v>116</v>
+      </c>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
       <c r="U17" s="4"/>
@@ -2226,7 +2290,7 @@
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9">
-        <v>934</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -2278,8 +2342,12 @@
       <c r="P18" s="4">
         <v>110</v>
       </c>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="4"/>
+      <c r="Q18" s="4">
+        <v>103</v>
+      </c>
+      <c r="R18" s="4">
+        <v>0</v>
+      </c>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
       <c r="U18" s="4"/>
@@ -2295,7 +2363,7 @@
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
       <c r="AG18" s="9">
-        <v>1075</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -2347,8 +2415,12 @@
       <c r="P19" s="4">
         <v>114</v>
       </c>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
+      <c r="Q19" s="4">
+        <v>111</v>
+      </c>
+      <c r="R19" s="4">
+        <v>0</v>
+      </c>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
       <c r="U19" s="4"/>
@@ -2364,7 +2436,7 @@
       <c r="AE19" s="4"/>
       <c r="AF19" s="4"/>
       <c r="AG19" s="9">
-        <v>1194</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -2416,8 +2488,12 @@
       <c r="P20" s="6">
         <v>1523</v>
       </c>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
+      <c r="Q20" s="6">
+        <v>1716</v>
+      </c>
+      <c r="R20" s="6">
+        <v>884</v>
+      </c>
       <c r="S20" s="6"/>
       <c r="T20" s="6"/>
       <c r="U20" s="6"/>
@@ -2433,7 +2509,7 @@
       <c r="AE20" s="6"/>
       <c r="AF20" s="6"/>
       <c r="AG20" s="10">
-        <v>20379</v>
+        <v>22979</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
@@ -2500,7 +2576,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.6262626262626263</v>
+        <v>3.1018518518518521</v>
       </c>
       <c r="D2" s="1"/>
     </row>
